--- a/docs/テストケース/単体テストケース・結果一覧表_画面_30分値データ登録.xlsx
+++ b/docs/テストケース/単体テストケース・結果一覧表_画面_30分値データ登録.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単体テストケース・結果一覧表" sheetId="1" r:id="Rf01fc7e08a6f46e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面共通項目チェック" sheetId="2" r:id="R052e3980c20a4de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="権限マトリクス" sheetId="3" r:id="R91a934b0ea684b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件マトリクス" sheetId="4" r:id="R8fa8d651aaf9459f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面定義書" sheetId="5" r:id="R4b6b8d9dda0c45d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提・実施方針" sheetId="6" r:id="Radae0f6c26c54e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単体テストケース・結果一覧表" sheetId="1" r:id="Rf453f81c107d4369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面共通項目チェック" sheetId="2" r:id="Rd9a3f790985a42fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="権限マトリクス" sheetId="3" r:id="R9fb797b324c54c08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件マトリクス" sheetId="4" r:id="R5b58987862544716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面定義書" sheetId="5" r:id="R866b2aec35524c25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提・実施方針" sheetId="6" r:id="Rb8f5e5130c3e4c8b"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'単体テストケース・結果一覧表'!$A$1:$O$39</x:definedName>
@@ -447,7 +447,7 @@
         <x:v>備　考</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
-        <x:v>結果欄は未実施のため空欄。複数条件は補助シートに個別結果を記入。静的解析・実施条件は「前提・実施方針」を参照。</x:v>
+        <x:v>結果欄は試験実施後に記入する。複数の条件は補助シートに個別の結果を記録する。静的解析と実施条件は「前提・実施方針」を参照する。</x:v>
       </x:c>
       <x:c r="H5" s="6"/>
       <x:c r="I5" s="6"/>
@@ -528,7 +528,7 @@
       <x:c r="N7" s="9"/>
       <x:c r="O7" s="9"/>
     </x:row>
-    <x:row r="8" ht="65" customHeight="1">
+    <x:row r="8" ht="75" customHeight="1">
       <x:c r="A8" s="10" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -539,7 +539,7 @@
         <x:v>サイドメニュー／利用可</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>権限マトリクスR01・R02の各利用者で確認する。</x:v>
+        <x:v>権限マトリクスのR01・R02の利用者で、サイドメニューの表示を確認する。</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
         <x:v>2</x:v>
@@ -548,12 +548,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
-        <x:v>①R01・R02の各利用者でログイン。
-②権限B5の設定を記録。
-③サイドメニューを表示する。</x:v>
+        <x:v>①R01とR02の利用者でそれぞれログインする。②権限B5の設定を記録する。③サイドメニューを確認する。</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>B5が利用可の各利用者に「電力30分値登録」が表示される。各利用者の確認結果を権限マトリクスへ記録する。</x:v>
+        <x:v>B5を利用できる各利用者には「電力30分値登録」が表示される。利用者ごとの結果を権限マトリクスに記録する。</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str"/>
       <x:c r="J8" s="10" t="str"/>
@@ -574,7 +572,7 @@
         <x:v>サイドメニュー／利用不可</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>権限マトリクスR03～R08のB5利用不可条件を確認する。</x:v>
+        <x:v>権限マトリクスのR03～R08で、B5を利用できない場合の表示を確認する。</x:v>
       </x:c>
       <x:c r="E9" s="10" t="n">
         <x:v>6</x:v>
@@ -583,11 +581,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
-        <x:v>①R03～R08の各利用者でログイン。
-②B5を利用不可とした条件でサイドメニューを確認。</x:v>
+        <x:v>①R03～R08の利用者でそれぞれログインする。②B5を利用できない状態でサイドメニューを確認する。</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>「電力30分値登録」が表示されない。利用者とB5の実設定を権限マトリクスに記録する。</x:v>
+        <x:v>「電力30分値登録」は表示されない。利用者とB5の設定値を権限マトリクスに記録する。</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str"/>
       <x:c r="J9" s="10" t="str"/>
@@ -617,11 +614,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
-        <x:v>①R01・R02でログイン。
-②「電力30分値登録」を押下。</x:v>
+        <x:v>①R01とR02の利用者でそれぞれログインする。②「電力30分値登録」を押す。</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>URLが /energy-building/ebmv01 となる。各利用者の画面遷移結果を権限マトリクスに記録する。</x:v>
+        <x:v>画面のURLが /energy-building/ebmv01 になる。利用者ごとの遷移結果を権限マトリクスに記録する。</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str"/>
       <x:c r="J10" s="10" t="str"/>
@@ -642,7 +638,7 @@
         <x:v>EP管理者</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>画面定義書の45項目を選択後の画面と照合する。</x:v>
+        <x:v>企業・拠点の選択後、画面定義書の45項目と画面表示を照合する。</x:v>
       </x:c>
       <x:c r="E11" s="10" t="n">
         <x:v>45</x:v>
@@ -651,12 +647,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
-        <x:v>①R01でログイン。
-②D01の企業・拠点を選択して戻る。CSVは未選択。
-③添付「画面定義書」の45項目を確認し、EP管理者欄に結果を記録。</x:v>
+        <x:v>①R01でログインする。②D01の企業と拠点を選択して登録画面に戻る。CSVは選択しない。③画面定義書の45項目を確認し、EP管理者欄に結果を記録する。</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>画面定義書のラベル、表示値、編集可否、ボタン状態、配置が一致する。No.の重複はセクションで識別する。</x:v>
+        <x:v>ラベル、表示値、編集可否、ボタンの状態、配置が画面定義書と一致する。番号が重複する項目はセクションで区別する。</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str">
         <x:v>○</x:v>
@@ -668,7 +662,7 @@
       <x:c r="N11" s="10" t="str"/>
       <x:c r="O11" s="10" t="str"/>
     </x:row>
-    <x:row r="12" ht="75" customHeight="1">
+    <x:row r="12" ht="65" customHeight="1">
       <x:c r="A12" s="10" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -679,7 +673,7 @@
         <x:v>EP担当者</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>画面定義書の45項目を選択後の画面と照合する。</x:v>
+        <x:v>企業・拠点の選択後、画面定義書の45項目と画面表示を照合する。</x:v>
       </x:c>
       <x:c r="E12" s="10" t="n">
         <x:v>45</x:v>
@@ -688,12 +682,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
-        <x:v>①R02でログイン。
-②D01の企業・拠点を選択して戻る。CSVは未選択。
-③添付「画面定義書」の45項目を確認し、EP担当者欄に結果を記録。</x:v>
+        <x:v>①R02でログインする。②D01の企業と拠点を選択して登録画面に戻る。CSVは選択しない。③画面定義書の45項目を確認し、EP担当者欄に結果を記録する。</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>EP管理者と同じ45項目が仕様どおり表示される。利用者を切り替えた初期画面HCを取得する。</x:v>
+        <x:v>EP管理者と同じ45項目が仕様どおり表示される。EP担当者でログインした画面のハードコピーを取得する。</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str">
         <x:v>○</x:v>
@@ -725,11 +717,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
-        <x:v>①selectedCorporateItem を削除。
-②登録画面を新規表示。</x:v>
+        <x:v>①selectedCorporateItemを削除する。②登録画面を新しく開く。</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>企業・拠点の値は未選択表示。CSV選択と登録は非活性。一覧取得APIを呼ばない。</x:v>
+        <x:v>企業と拠点は未選択の状態で表示される。CSV選択と登録の操作はできず、一覧取得APIは呼び出されない。</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str">
         <x:v>○</x:v>
@@ -763,12 +754,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
-        <x:v>①企業情報の「選択」を押下。
-②/energy-building/ebmv02 でD01を選択。
-③登録画面へ戻る。</x:v>
+        <x:v>①企業情報の「選択」を押す。②/energy-building/ebmv02 でD01を選択する。③登録画面に戻る。</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
-        <x:v>選択画面へ遷移し、戻った後はD01の基本情報・拠点情報・同意書取得経路が表示される。</x:v>
+        <x:v>選択画面へ遷移する。登録画面に戻ると、D01の企業基本情報、拠点情報、同意書取得経路が表示される。</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str"/>
       <x:c r="J14" s="10" t="str"/>
@@ -800,12 +789,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
-        <x:v>①D01を選択。
-②selectedCorporateItem と画面の9項目を比較。
-③所在地は都道府県と市区町村を比較。</x:v>
+        <x:v>①D01を選択する。②selectedCorporateItemと画面の9項目を比較する。③所在地は都道府県と市区町村を組み合わせた値で確認する。</x:v>
       </x:c>
       <x:c r="H15" s="6" t="str">
-        <x:v>お客さま名、法人番号、本社所在地、拠点名、拠点所在地、事業所コード、お客さま番号、供給地点特定番号、同意書取得経路が選択値と一致。所在地は都道府県＋市区町村。</x:v>
+        <x:v>お客さま名、法人番号、本社所在地、拠点名、拠点所在地、事業所コード、お客さま番号、供給地点特定番号、同意書取得経路が選択値と一致する。所在地には都道府県と市区町村が表示される。</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str"/>
       <x:c r="J15" s="10" t="str"/>
@@ -817,7 +804,7 @@
       <x:c r="N15" s="10" t="str"/>
       <x:c r="O15" s="10" t="str"/>
     </x:row>
-    <x:row r="16" ht="75" customHeight="1">
+    <x:row r="16" ht="100" customHeight="1">
       <x:c r="A16" s="10" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -837,11 +824,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
-        <x:v>①D01を選択。
-②開発者ツールのNetworkで一覧取得リクエストを保存。</x:v>
+        <x:v>①D01を選択する。②開発者ツールのNetworkで一覧取得リクエストを保存する。</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
-        <x:v>GET /api/building/per_30min_data の4パラメータがC1・B20・01・O1の実値と一致。JSON本文ではなくクエリとして渡す。</x:v>
+        <x:v>GET /api/building/per_30min_data の法人番号、拠点ID、同意区分、組織IDが、C1・B20・01・O1の実値と一致する。4項目はJSON本文ではなくクエリとして送られる。</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str"/>
       <x:c r="J16" s="10" t="str"/>
@@ -873,12 +859,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
-        <x:v>①D01を表示。
-②選択画面でD02へ変更して戻る。
-③通信記録と一覧を比較。</x:v>
+        <x:v>①D01を表示する。②選択画面でD02に切り替えて戻る。③通信記録と一覧表示を比較する。</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
-        <x:v>building_idがB10へ変わり、表示はD02の期間20260103～20260103となる。D01の情報が残らない。</x:v>
+        <x:v>building_idはB10に変わり、D02の期間20260103～20260103が表示される。D01の情報は残らない。</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str"/>
       <x:c r="J17" s="10" t="str"/>
@@ -890,7 +874,7 @@
       <x:c r="N17" s="10" t="str"/>
       <x:c r="O17" s="10" t="str"/>
     </x:row>
-    <x:row r="18" ht="100" customHeight="1">
+    <x:row r="18" ht="125" customHeight="1">
       <x:c r="A18" s="10" t="n">
         <x:v>11</x:v>
       </x:c>
@@ -910,11 +894,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
-        <x:v>①D01を取得。
-②API応答とARVE3列を比較。</x:v>
+        <x:v>①D01の一覧を取得する。②API応答とARVEの3項目を比較する。</x:v>
       </x:c>
       <x:c r="H18" s="6" t="str">
-        <x:v>ARVEお客さま名=ARVE試験会社、事業所コード=012、お客さま番号=0000000000045。キーはそれぞれARVE_CORP_NAME、ARVE_OFFICE_CODE、ARVE_CUSTOMER_NUMBER。先頭ゼロを保持。</x:v>
+        <x:v>ARVEお客さま名は「ARVE試験会社」、事業所コードは「012」、お客さま番号は「0000000000045」と表示される。対応するキーはARVE_CORP_NAME、ARVE_OFFICE_CODE、ARVE_CUSTOMER_NUMBERであり、先頭のゼロは保持される。</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str"/>
       <x:c r="J18" s="10" t="str"/>
@@ -926,7 +909,7 @@
       <x:c r="N18" s="10" t="str"/>
       <x:c r="O18" s="10" t="str"/>
     </x:row>
-    <x:row r="19" ht="75" customHeight="1">
+    <x:row r="19" ht="87.5" customHeight="1">
       <x:c r="A19" s="10" t="n">
         <x:v>12</x:v>
       </x:c>
@@ -946,11 +929,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
-        <x:v>①D01を取得。
-②API応答の期間と日時を画面と比較。</x:v>
+        <x:v>①D01の一覧を取得する。②API応答の期間と日時を画面表示と比較する。</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
-        <x:v>開始2026/01/02、終了2026/01/04、登録・更新日時2026/01/05 10:20:30。日付はスラッシュ、時刻はコロン区切り。</x:v>
+        <x:v>開始日は2026/01/02、終了日は2026/01/04、登録・更新日時は2026/01/05 10:20:30と表示される。日付はスラッシュ、時刻はコロンで区切られる。</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str"/>
       <x:c r="J19" s="10" t="str"/>
@@ -982,11 +964,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
-        <x:v>①D01の取得日を20261231と20270101に変更。
-②再取得する。</x:v>
+        <x:v>①D01の取得日を20261231と20270101に変更する。②一覧を再取得する。</x:v>
       </x:c>
       <x:c r="H20" s="6" t="str">
-        <x:v>開始2026/12/31、終了2027/01/01。年月日が欠落・入替わりしない。</x:v>
+        <x:v>開始日は2026/12/31、終了日は2027/01/01と表示される。年月日の欠落や入れ替わりはない。</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str"/>
       <x:c r="J20" s="10" t="str"/>
@@ -1016,11 +997,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
-        <x:v>①D01の取得日を20240229の1行にする。
-②再取得する。</x:v>
+        <x:v>①D01の取得日を20240229の1行にする。②一覧を再取得する。</x:v>
       </x:c>
       <x:c r="H21" s="6" t="str">
-        <x:v>開始・終了とも2024/02/29。3月1日等へ変換しない。</x:v>
+        <x:v>開始日と終了日の両方に2024/02/29が表示される。3月1日など別の日付には変換されない。</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str"/>
       <x:c r="J21" s="10" t="str"/>
@@ -1030,7 +1010,7 @@
       <x:c r="N21" s="10" t="str"/>
       <x:c r="O21" s="10" t="str"/>
     </x:row>
-    <x:row r="22" ht="65" customHeight="1">
+    <x:row r="22" ht="75" customHeight="1">
       <x:c r="A22" s="10" t="n">
         <x:v>15</x:v>
       </x:c>
@@ -1050,12 +1030,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>①D01のARVE3項目をNULLにして取得。
-②空文字にして取得。
-③条件マトリクスS15に各結果を記録。</x:v>
+        <x:v>①D01のARVEの3項目をすべてNULLにして取得する。②3項目をすべて空文字にして取得する。③各結果を条件マトリクスS15に記録する。</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
-        <x:v>両条件で3列が空欄。null・undefinedの文字は表示しない。他列はD01の値を保持する。</x:v>
+        <x:v>どちらの条件でも3項目は空欄になり、「null」や「undefined」という文字は表示されない。ほかの列にはD01の値が表示される。</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str"/>
       <x:c r="J22" s="10" t="str"/>
@@ -1085,11 +1063,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>①一覧応答のfile_update_dateだけをnullにしたスタブを返す。
-②画面表示を確認する。</x:v>
+        <x:v>①一覧応答のfile_update_dateだけをnullにしたスタブを返す。②画面表示を確認する。</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
-        <x:v>登録・更新日時は「--/--/-- --:--:--」。画面全体は表示を継続する。補足：画面側の防御分岐を確認するケース。</x:v>
+        <x:v>登録・更新日時には「--/--/-- --:--:--」が表示され、画面はそのまま利用できる。画面側の防御処理を確認する。</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str"/>
       <x:c r="J23" s="10" t="str"/>
@@ -1099,7 +1076,7 @@
       <x:c r="N23" s="10" t="str"/>
       <x:c r="O23" s="10" t="str"/>
     </x:row>
-    <x:row r="24" ht="75" customHeight="1">
+    <x:row r="24" ht="87.5" customHeight="1">
       <x:c r="A24" s="10" t="n">
         <x:v>17</x:v>
       </x:c>
@@ -1119,10 +1096,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>①D01の生データを0件にして取得。</x:v>
+        <x:v>①D01の生データを0件にする。②一覧を取得する。</x:v>
       </x:c>
       <x:c r="H24" s="6" t="str">
-        <x:v>データ行は0件。「該当するデータが見つかりません。」を表示。旧行が残らない。件数・ページ操作は非表示（共通テーブルの既存仕様）。</x:v>
+        <x:v>データ行は表示されず、「該当するデータが見つかりません。」と表示される。以前の行は残らず、共通テーブルの既存仕様どおり件数とページ操作も表示されない。</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str">
         <x:v>○</x:v>
@@ -1156,11 +1133,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
-        <x:v>①一覧応答スタブで開始20260101、20260201の2行をこの順で返す。
-②ヘッダーをクリックせず確認。</x:v>
+        <x:v>①開始日が20260101と20260201の2行を、この順序で一覧応答スタブから返す。②ヘッダーを押さずに表示順を確認する。</x:v>
       </x:c>
       <x:c r="H25" s="6" t="str">
-        <x:v>20260101、20260201の順。画面で自動的に降順へ並べ替えない。</x:v>
+        <x:v>2行は20260101、20260201の順に表示される。画面側で自動的に降順へ並べ替えられない。</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str"/>
       <x:c r="J25" s="10" t="str"/>
@@ -1172,7 +1148,7 @@
       <x:c r="N25" s="10" t="str"/>
       <x:c r="O25" s="10" t="str"/>
     </x:row>
-    <x:row r="26" ht="75" customHeight="1">
+    <x:row r="26" ht="100" customHeight="1">
       <x:c r="A26" s="10" t="n">
         <x:v>19</x:v>
       </x:c>
@@ -1192,12 +1168,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str">
-        <x:v>①応答スタブに0・1・5・6行を順に設定。
-②行数は5に設定。
-③条件マトリクスS19に結果を記録。</x:v>
+        <x:v>①一覧応答スタブの行数を0・1・5・6行に順次変える。②1ページの表示行数を5にする。③各結果を条件マトリクスS19に記録する。</x:v>
       </x:c>
       <x:c r="H26" s="6" t="str">
-        <x:v>0件は該当なし表示。1・5件は1ページ、6件は2ページ。2ページ目は6行目だけ。次／前ボタンの活性が境界と一致。</x:v>
+        <x:v>0件では該当なしのメッセージを表示する。1件と5件では1ページ、6件では2ページになり、2ページ目には6行目だけが表示される。前後の移動ボタンの状態もページ境界に一致する。</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str"/>
       <x:c r="J26" s="10" t="str"/>
@@ -1207,7 +1181,7 @@
       <x:c r="N26" s="10" t="str"/>
       <x:c r="O26" s="10" t="str"/>
     </x:row>
-    <x:row r="27" ht="65" customHeight="1">
+    <x:row r="27" ht="87.5" customHeight="1">
       <x:c r="A27" s="10" t="n">
         <x:v>20</x:v>
       </x:c>
@@ -1227,12 +1201,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G27" s="6" t="str">
-        <x:v>①固有の51行を返すスタブを使用。
-②行数5・10・20・50を順に選択。
-③条件マトリクスS20に結果を記録。</x:v>
+        <x:v>①異なる内容の51行を返すスタブを使用する。②表示行数を5・10・20・50に順次変える。③各結果を条件マトリクスS20に記録する。</x:v>
       </x:c>
       <x:c r="H27" s="6" t="str">
-        <x:v>1ページ目の件数範囲は各1～5／10／20／50。総ページは11／6／3／2。行数変更時は1ページ目へ戻る。</x:v>
+        <x:v>1ページ目には、それぞれ1～5件、1～10件、1～20件、1～50件が表示される。総ページ数は順に11・6・3・2で、表示行数を変えると1ページ目に戻る。</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str"/>
       <x:c r="J27" s="10" t="str"/>
@@ -1242,7 +1214,7 @@
       <x:c r="N27" s="10" t="str"/>
       <x:c r="O27" s="10" t="str"/>
     </x:row>
-    <x:row r="28" ht="65" customHeight="1">
+    <x:row r="28" ht="87.5" customHeight="1">
       <x:c r="A28" s="10" t="n">
         <x:v>21</x:v>
       </x:c>
@@ -1253,7 +1225,7 @@
         <x:v>ページ移動</x:v>
       </x:c>
       <x:c r="D28" s="6" t="str">
-        <x:v>先頭・前・次・末尾の移動で重複／欠落がない。</x:v>
+        <x:v>先頭・前・次・末尾へ移動しても、行の重複や欠落がないことを確認する。</x:v>
       </x:c>
       <x:c r="E28" s="10" t="n">
         <x:v>1</x:v>
@@ -1262,11 +1234,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
-        <x:v>①12行スタブ、行数5。
-②次→末尾→前→先頭を順に押下。</x:v>
+        <x:v>①12行を返すスタブを使い、表示行数を5にする。②「次」「末尾」「前」「先頭」の順に押す。</x:v>
       </x:c>
       <x:c r="H28" s="6" t="str">
-        <x:v>表示範囲は6～10→11～12→6～10→1～5。先頭では先頭／前、末尾では次／末尾が非活性。</x:v>
+        <x:v>表示範囲は6～10件、11～12件、6～10件、1～5件の順に変わる。先頭ページでは「先頭」「前」、末尾ページでは「次」「末尾」が押せない。</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str"/>
       <x:c r="J28" s="10" t="str"/>
@@ -1276,7 +1247,7 @@
       <x:c r="N28" s="10" t="str"/>
       <x:c r="O28" s="10" t="str"/>
     </x:row>
-    <x:row r="29" ht="75" customHeight="1">
+    <x:row r="29" ht="87.5" customHeight="1">
       <x:c r="A29" s="10" t="n">
         <x:v>22</x:v>
       </x:c>
@@ -1296,11 +1267,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G29" s="6" t="str">
-        <x:v>①ARVEお客さま名1300文字、コード3文字、番号16文字のスタブを返す。
-②スクロールを含めて確認。</x:v>
+        <x:v>①ARVEお客さま名が1300文字、コードが3文字、番号が16文字の応答スタブを返す。②スクロールした部分も確認する。</x:v>
       </x:c>
       <x:c r="H29" s="6" t="str">
-        <x:v>文字化けや隣列への重なりがない。元の文字列を画面上で確認できる。桁数はEntity定義に基づく表示試験であり入力制約ではない。</x:v>
+        <x:v>文字化けや隣の列への重なりがなく、元の文字列を画面で確認できる。この桁数はEntity定義に基づく表示確認に用い、入力制約の判定には用いない。</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str"/>
       <x:c r="J29" s="10" t="str"/>
@@ -1310,7 +1280,7 @@
       <x:c r="N29" s="10" t="str"/>
       <x:c r="O29" s="10" t="str"/>
     </x:row>
-    <x:row r="30" ht="65" customHeight="1">
+    <x:row r="30" ht="75" customHeight="1">
       <x:c r="A30" s="10" t="n">
         <x:v>23</x:v>
       </x:c>
@@ -1330,11 +1300,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G30" s="6" t="str">
-        <x:v>①D01選択後、ファイル未選択で登録ボタン状態を確認。
-②ファイルダイアログを開いて取消。</x:v>
+        <x:v>①D01を選択し、ファイルを選ばずに登録ボタンの状態を確認する。②ファイル選択ダイアログを開いて取り消す。</x:v>
       </x:c>
       <x:c r="H30" s="6" t="str">
-        <x:v>登録ボタンは非活性のまま。登録APIを呼ばない。未選択エラーを出すための非活性ボタン操作は行わない。</x:v>
+        <x:v>登録ボタンは押せないままで、登録APIは呼び出されない。押せないボタンから未選択エラーを表示させる操作は行わない。</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str"/>
       <x:c r="J30" s="10" t="str"/>
@@ -1366,10 +1335,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G31" s="6" t="str">
-        <x:v>①D01選択後、既存の正常サンプルをUT30_valid.csvとして選択。</x:v>
+        <x:v>①D01を選択する。②既存の正常サンプルをUT30_valid.csvという名前で選ぶ。</x:v>
       </x:c>
       <x:c r="H31" s="6" t="str">
-        <x:v>ファイル名がUT30_valid.csvとなり、登録ボタンが活性化する。ファイル名は手入力できない。</x:v>
+        <x:v>ファイル名にUT30_valid.csvが表示され、登録ボタンを押せるようになる。ファイル名は手入力できない。</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str"/>
       <x:c r="J31" s="10" t="str"/>
@@ -1379,7 +1348,7 @@
       <x:c r="N31" s="10" t="str"/>
       <x:c r="O31" s="10" t="str"/>
     </x:row>
-    <x:row r="32" ht="75" customHeight="1">
+    <x:row r="32" ht="87.5" customHeight="1">
       <x:c r="A32" s="10" t="n">
         <x:v>25</x:v>
       </x:c>
@@ -1399,12 +1368,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G32" s="6" t="str">
-        <x:v>①ファイル選択イベントをスタブしUT30.txt(text/plain)を指定。
-②UT30.csv(application/pdf)も指定して登録を押下。
-③条件マトリクスS25へ記録。</x:v>
+        <x:v>①ファイル選択イベントをスタブし、UT30.txt（text/plain）を指定する。②UT30.csv（application/pdf）も指定して登録を押す。③各結果を条件マトリクスS25に記録する。</x:v>
       </x:c>
       <x:c r="H32" s="6" t="str">
-        <x:v>「アップロードできるファイル形式はcsvのみです。」を表示。両条件で確認ダイアログと登録API呼出しはない。</x:v>
+        <x:v>どちらの条件でも「アップロードできるファイル形式はcsvのみです。」と表示される。確認ダイアログは開かず、登録APIも呼び出されない。</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str">
         <x:v>○</x:v>
@@ -1418,7 +1385,7 @@
       <x:c r="N32" s="10" t="str"/>
       <x:c r="O32" s="10" t="str"/>
     </x:row>
-    <x:row r="33" ht="65" customHeight="1">
+    <x:row r="33" ht="87.5" customHeight="1">
       <x:c r="A33" s="10" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -1438,11 +1405,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G33" s="6" t="str">
-        <x:v>①正常CSVを選択し登録を押下。
-②確認画面を保存して「いいえ」を押下。</x:v>
+        <x:v>①正常なCSVを選んで登録を押す。②確認ダイアログを保存し、「いいえ」を押す。</x:v>
       </x:c>
       <x:c r="H33" s="6" t="str">
-        <x:v>「電力30分値を登録します。よろしいですか？」を表示。取消後はファイル選択を保持し、POSTしない。</x:v>
+        <x:v>「電力30分値を登録します。よろしいですか？」と表示される。「いいえ」を押した後も選択したファイルは保持され、POSTリクエストは送られない。</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str">
         <x:v>○</x:v>
@@ -1456,7 +1422,7 @@
       <x:c r="N33" s="10" t="str"/>
       <x:c r="O33" s="10" t="str"/>
     </x:row>
-    <x:row r="34" ht="100" customHeight="1">
+    <x:row r="34" ht="125" customHeight="1">
       <x:c r="A34" s="10" t="n">
         <x:v>27</x:v>
       </x:c>
@@ -1476,12 +1442,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G34" s="6" t="str">
-        <x:v>①D01と正常CSVを選択。
-②登録→「はい」。
-③POSTの本文を保存しBase64を復号して元ファイルと比較。</x:v>
+        <x:v>①D01と正常なCSVを選ぶ。②登録を押し、確認ダイアログで「はい」を選ぶ。③POSTリクエストの本文を保存し、Base64を復号して元ファイルと比較する。</x:v>
       </x:c>
       <x:c r="H34" s="6" t="str">
-        <x:v>/api/file/per-30m-dataにcorp_number/building_id/org_id/agreement_categoryがC1/B20/O1/01。EPコード・番号・供給地点・企業名・拠点名もD01と一致。復号CSVは元と一致。</x:v>
+        <x:v>/api/file/per-30m-data に送るcorp_number、building_id、org_id、agreement_categoryがC1・B20・O1・01と一致する。EPコード・番号・供給地点・企業名・拠点名もD01と一致し、復号したCSVは元ファイルと同じ内容になる。</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str"/>
       <x:c r="J34" s="10" t="str"/>
@@ -1493,7 +1457,7 @@
       <x:c r="N34" s="10" t="str"/>
       <x:c r="O34" s="10" t="str"/>
     </x:row>
-    <x:row r="35" ht="75" customHeight="1">
+    <x:row r="35" ht="100" customHeight="1">
       <x:c r="A35" s="10" t="n">
         <x:v>28</x:v>
       </x:c>
@@ -1513,11 +1477,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G35" s="6" t="str">
-        <x:v>①正常CSVを登録。
-②登録APIは成功、一覧APIは期間20260101～20260131を返す。</x:v>
+        <x:v>①正常なCSVを登録する。②登録APIを成功させ、一覧APIから期間20260101～20260131を返す。</x:v>
       </x:c>
       <x:c r="H35" s="6" t="str">
-        <x:v>登録成功通知が表示される。同じ4条件でGETし、期間は2026/01/01～2026/01/31へ更新。ファイル選択が解除され登録は非活性。</x:v>
+        <x:v>登録成功の通知が表示される。同じ4条件で一覧取得APIが呼ばれ、期間は2026/01/01～2026/01/31に更新される。ファイルの選択は解除され、登録ボタンは押せなくなる。</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str">
         <x:v>○</x:v>
@@ -1531,7 +1494,7 @@
       <x:c r="N35" s="10" t="str"/>
       <x:c r="O35" s="10" t="str"/>
     </x:row>
-    <x:row r="36" ht="65" customHeight="1">
+    <x:row r="36" ht="87.5" customHeight="1">
       <x:c r="A36" s="10" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -1551,11 +1514,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G36" s="6" t="str">
-        <x:v>①正常CSVを登録。
-②POSTを500、message=システムエラーが発生しました。で応答させる。</x:v>
+        <x:v>①正常なCSVを登録する。②POSTリクエストにHTTP 500、message=システムエラーが発生しました。を返す。</x:v>
       </x:c>
       <x:c r="H36" s="6" t="str">
-        <x:v>当該エラーメッセージを表示。成功通知を表示しない。結果は未実施とし、失敗時は欠陥を記録する。</x:v>
+        <x:v>該当するエラーメッセージが表示され、成功通知は表示されない。結果欄は実施前に記入せず、期待結果と異なる場合は欠陥として記録する。</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str">
         <x:v>○</x:v>
@@ -1589,13 +1551,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G37" s="6" t="str">
-        <x:v>①D01を表示。
-②再取得を500にする。
-③同じ操作でネットワークを失敗させる。
-④条件マトリクスS30へ記録。</x:v>
+        <x:v>①D01を表示する。②一覧の再取得にHTTP 500を返す。③同じ操作でネットワーク障害を発生させる。④各結果を条件マトリクスS30に記録する。</x:v>
       </x:c>
       <x:c r="H37" s="6" t="str">
-        <x:v>「データの取得に失敗しました。」を表示。旧一覧の行を消去し、処理待ちのままにならない。</x:v>
+        <x:v>どちらの条件でも「データの取得に失敗しました。」と表示される。以前の一覧行は消え、読み込み中の状態が続かない。</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str">
         <x:v>○</x:v>
@@ -1609,7 +1568,7 @@
       <x:c r="N37" s="10" t="str"/>
       <x:c r="O37" s="10" t="str"/>
     </x:row>
-    <x:row r="38" ht="75" customHeight="1">
+    <x:row r="38" ht="87.5" customHeight="1">
       <x:c r="A38" s="10" t="n">
         <x:v>31</x:v>
       </x:c>
@@ -1629,11 +1588,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G38" s="6" t="str">
-        <x:v>①D01選択後にブラウザを再読込。
-②sessionStorageとAPI呼出しを確認。</x:v>
+        <x:v>①D01を選択してからブラウザを再読み込みする。②sessionStorageとAPIの呼び出しを確認する。</x:v>
       </x:c>
       <x:c r="H38" s="6" t="str">
-        <x:v>selectedCorporateItemが削除され、未選択状態になる。古い拠点のGETを行わない。補足：既存セッション消去処理の回帰確認。</x:v>
+        <x:v>selectedCorporateItemが削除され、企業・拠点は未選択になる。以前の拠点を対象とするGETリクエストは送られない。既存のセッション消去処理を確認する。</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str"/>
       <x:c r="J38" s="10" t="str"/>
@@ -1665,12 +1623,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G39" s="6" t="str">
-        <x:v>①selectedCorporateItemに不正JSON「{」を設定。
-②再読込イベントを避けて登録画面へ遷移。
-③コンソールを保存。</x:v>
+        <x:v>①selectedCorporateItemに不正なJSON「{」を設定する。②再読み込みイベントを避けて登録画面へ遷移する。③コンソールの記録を保存する。</x:v>
       </x:c>
       <x:c r="H39" s="6" t="str">
-        <x:v>未選択状態で画面表示を継続し、一覧GETを行わない。セッション取得エラーをコンソールへ記録する。</x:v>
+        <x:v>画面は未選択の状態で表示を続け、一覧取得のGETリクエストは送られない。セッション取得時のエラーがコンソールに記録される。</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str"/>
       <x:c r="J39" s="10" t="str"/>
@@ -2880,10 +2836,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
-        <x:v>ARVE3項目=NULL</x:v>
+        <x:v>ARVEの3項目をすべてNULLにする。</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>3列空欄。他列を保持。</x:v>
+        <x:v>3項目は空欄になり、ほかの列には元の値が表示される。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str"/>
       <x:c r="F4" s="6" t="str"/>
@@ -2897,10 +2853,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>ARVE3項目=空文字</x:v>
+        <x:v>ARVEの3項目をすべて空文字にする。</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>3列空欄。他列を保持。</x:v>
+        <x:v>3項目は空欄になり、ほかの列には元の値が表示される。</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str"/>
       <x:c r="F5" s="6" t="str"/>
@@ -2914,10 +2870,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>応答0行／行数5</x:v>
+        <x:v>応答を0行とし、表示行数を5にする。</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>該当なしメッセージ。ページ表示なし。</x:v>
+        <x:v>該当なしのメッセージを表示し、ページ操作は表示しない。</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str"/>
       <x:c r="F6" s="6" t="str"/>
@@ -2931,10 +2887,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
-        <x:v>応答1行／行数5</x:v>
+        <x:v>応答を1行とし、表示行数を5にする。</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>1件／1ページ。末尾ページ1～1件。</x:v>
+        <x:v>1件を1ページに表示する。</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str"/>
       <x:c r="F7" s="6" t="str"/>
@@ -2948,10 +2904,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>応答5行／行数5</x:v>
+        <x:v>応答を5行とし、表示行数を5にする。</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>5件／1ページ。末尾ページ1～5件。</x:v>
+        <x:v>5件を1ページに表示する。</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str"/>
       <x:c r="F8" s="6" t="str"/>
@@ -2965,10 +2921,10 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>応答6行／行数5</x:v>
+        <x:v>応答を6行とし、表示行数を5にする。</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>6件／2ページ。末尾ページ6～6件。</x:v>
+        <x:v>2ページになり、2ページ目には6行目だけが表示される。</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str"/>
       <x:c r="F9" s="6" t="str"/>
@@ -2982,10 +2938,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
-        <x:v>応答51行／行数5</x:v>
+        <x:v>応答を51行とし、表示行数を5にする。</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>1～5件、11ページ。変更後1ページ目。</x:v>
+        <x:v>1ページ目には1～5件を表示し、総ページ数は11になる。</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str"/>
       <x:c r="F10" s="6" t="str"/>
@@ -2999,10 +2955,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>応答51行／行数10</x:v>
+        <x:v>応答を51行とし、表示行数を10にする。</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>1～10件、6ページ。変更後1ページ目。</x:v>
+        <x:v>1ページ目には1～10件を表示し、総ページ数は6になる。</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str"/>
       <x:c r="F11" s="6" t="str"/>
@@ -3016,10 +2972,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
-        <x:v>応答51行／行数20</x:v>
+        <x:v>応答を51行とし、表示行数を20にする。</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>1～20件、3ページ。変更後1ページ目。</x:v>
+        <x:v>1ページ目には1～20件を表示し、総ページ数は3になる。</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str"/>
       <x:c r="F12" s="6" t="str"/>
@@ -3033,16 +2989,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>応答51行／行数50</x:v>
+        <x:v>応答を51行とし、表示行数を50にする。</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>1～50件、2ページ。変更後1ページ目。</x:v>
+        <x:v>1ページ目には1～50件を表示し、総ページ数は2になる。</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str"/>
       <x:c r="F13" s="6" t="str"/>
       <x:c r="G13" s="6" t="str"/>
     </x:row>
-    <x:row r="14" ht="28" customHeight="1">
+    <x:row r="14" ht="37.5" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>S25-1</x:v>
       </x:c>
@@ -3050,16 +3006,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
-        <x:v>UT30.txt(text/plain)</x:v>
+        <x:v>UT30.txtをtext/plainとして選択する。</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>CSV形式エラー、POSTなし。画面HC取得。</x:v>
+        <x:v>CSV形式のエラーを表示し、POSTリクエストは送られない。画面のハードコピーを取得する。</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str"/>
       <x:c r="F14" s="6" t="str"/>
       <x:c r="G14" s="6" t="str"/>
     </x:row>
-    <x:row r="15" ht="28" customHeight="1">
+    <x:row r="15" ht="37.5" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>S25-2</x:v>
       </x:c>
@@ -3067,16 +3023,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="6" t="str">
-        <x:v>UT30.csv(application/pdf)</x:v>
+        <x:v>UT30.csvをapplication/pdfとして選択する。</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>CSV形式エラー、POSTなし。画面HC取得。</x:v>
+        <x:v>CSV形式のエラーを表示し、POSTリクエストは送られない。画面のハードコピーを取得する。</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str"/>
       <x:c r="F15" s="6" t="str"/>
       <x:c r="G15" s="6" t="str"/>
     </x:row>
-    <x:row r="16" ht="28" customHeight="1">
+    <x:row r="16" ht="37.5" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>S30-1</x:v>
       </x:c>
@@ -3084,16 +3040,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="6" t="str">
-        <x:v>HTTP 500</x:v>
+        <x:v>一覧取得APIからHTTP 500を返す。</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
-        <x:v>取得失敗メッセージ、旧一覧消去。画面HC取得。</x:v>
+        <x:v>取得失敗のメッセージを表示し、以前の一覧を消す。画面のハードコピーを取得する。</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str"/>
       <x:c r="F16" s="6" t="str"/>
       <x:c r="G16" s="6" t="str"/>
     </x:row>
-    <x:row r="17" ht="28" customHeight="1">
+    <x:row r="17" ht="37.5" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>S30-2</x:v>
       </x:c>
@@ -3101,10 +3057,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C17" s="6" t="str">
-        <x:v>ネットワーク失敗</x:v>
+        <x:v>一覧取得APIでネットワーク障害を発生させる。</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>取得失敗メッセージ、旧一覧消去。画面HC取得。</x:v>
+        <x:v>取得失敗のメッセージを表示し、以前の一覧を消す。画面のハードコピーを取得する。</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str"/>
       <x:c r="F17" s="6" t="str"/>
@@ -5208,7 +5164,7 @@
         <x:v>開始／完了</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>ソースレビュー・静的解析をクリアして開始。全実行条件の消化率100％、未解決欠陥0件で完了。結果・実施日・実施者は実行後に記録する。</x:v>
+        <x:v>ソースレビューと静的解析を完了してから試験を始める。すべての条件を実施し、未解決の欠陥が0件になった時点で完了とする。結果・実施日・実施者は試験後に記録する。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="37.5" customHeight="1">
@@ -5216,7 +5172,7 @@
         <x:v>自動テスト</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>計画書でPytest・C0/C1 90％を要求する対象は指定の2バッチ。本画面／APIには一律のカバレッジ基準を設定しない。既存のPytest 2件だけで手動ケースをOKにしない。</x:v>
+        <x:v>計画書でPytestとC0/C1のカバレッジ90％以上が求められるのは、指定された2つのバッチである。この画面とAPIには一律のカバレッジ基準を設けない。既存のPytest 2件が成功しても、手動試験を完了した扱いにはしない。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="37.5" customHeight="1">
@@ -5224,7 +5180,7 @@
         <x:v>静的解析</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>画面はESLint、バックエンドはFlake8。命名、未使用import/変数、any・型アサーション、useEffect依存、三項演算子ネスト、JSX／PEP8、行長、構文、空白、複雑度を確認。</x:v>
+        <x:v>画面ではESLint、バックエンドではFlake8を使う。命名、未使用のimport・変数、any・型アサーション、useEffectの依存関係、三項演算子の入れ子、JSX・PEP8、行の長さ、構文、空白、複雑度を確認する。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="37.5" customHeight="1">
@@ -5232,7 +5188,7 @@
         <x:v>静的解析の記録</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>実行コマンド・ツール設定・対象ファイル・実行日時・ログ保存先・STEP3ベースラインとの差分・残指摘対応を記録する。修正不可はTEPSYS協議の許容記録を残す。静的解析結果：未実施。</x:v>
+        <x:v>実行コマンド、ツールの設定、対象ファイル、実行日時、ログの保存先、STEP3時点との差分、残る指摘への対応を記録する。修正できない指摘は、TEPSYSと協議した許容記録を残す。静的解析は未実施である。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -5240,7 +5196,7 @@
         <x:v>STEP3との差分</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>STEP4変更前の検出内容を保持し、新規・変更箇所の差分を対象とする。既存指摘を無条件に改修対象へ含めない。</x:v>
+        <x:v>STEP4の変更前に検出された内容を保持し、新規・変更箇所との差分を確認する。既存の指摘を無条件に改修対象へ加えない。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="37.5" customHeight="1">
@@ -5248,7 +5204,7 @@
         <x:v>ケース数と結果</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
-        <x:v>一覧のケース数は実行する条件数。複数条件は条件マトリクス、権限は権限マトリクス、初期表示45項目は画面定義書に個別結果を記録。行の結果は全条件消化後に記入する。</x:v>
+        <x:v>一覧のケース数は、実行する条件の数を示す。複数条件は条件マトリクス、権限は権限マトリクス、初期表示の45項目は画面定義書に個別の結果を記録する。各ケースの結果は、すべての条件を実施した後に記入する。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="37.5" customHeight="1">
@@ -5256,7 +5212,7 @@
         <x:v>証跡</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>初期表示とメッセージ表示は画面HCを取得。画面共通項目チェックは目視確認のみでHC不要。API入出力は通信記録、DB照合は対象行ダンプ、ログは実行時刻を対応させて保存。</x:v>
+        <x:v>初期表示とメッセージ表示では画面のハードコピーを取得する。画面共通項目チェックは目視で確認し、ハードコピーは不要とする。APIの入出力は通信記録、DBの照合は対象行のダンプで確認する。ログは実行時刻と対応づけて保存する。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="37.5" customHeight="1">
@@ -5272,7 +5228,7 @@
         <x:v>データ方針</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>STEP3開発環境マスタ・受領済サンプルを優先再利用。不足するトランザクションのみ追加する。C1/C2/O1/O2/B20/B10は論理識別子であり、下の対応欄に実IDを記入してから実施する。</x:v>
+        <x:v>STEP3の開発環境マスタと受領済みのサンプルを優先して再利用し、不足するトランザクションだけを追加する。C1/C2/O1/O2/B20/B10は論理識別子なので、下の対応欄に実際のIDを記入してから試験する。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="37.5" customHeight="1">
@@ -5280,7 +5236,7 @@
         <x:v>独立再実行</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
-        <x:v>各ケース前にD01等の指定データを再準備し、対象行の前後ダンプを採取。検証用に変更した行は保存した状態へ戻す。他ケースの実行順に依存させない。</x:v>
+        <x:v>各ケースの前にD01などの指定データを準備し、対象行の実施前後のダンプを取得する。検証のために変更した行は元の状態へ戻し、ほかのケースの実行順に依存しないようにする。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
@@ -5312,7 +5268,7 @@
         <x:v>ユーザー</x:v>
       </x:c>
       <x:c r="B18" s="6" t="str">
-        <x:v>R01等の試験ユーザーID・組織・権限は権限マトリクスに記入。既存ユーザーを使用。APIの対象外ロールは認証後コンテキストをスタブしてもよい。</x:v>
+        <x:v>R01などの試験ユーザーID・組織・権限は権限マトリクスに記入する。試験には既存ユーザーを使用する。APIの対象外ロールは、認証後のコンテキストをスタブして確認してもよい。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="37.5" customHeight="1">
@@ -5387,12 +5343,12 @@
         <x:v>画面：docs/仕様/画面設計書_30分値データ登録画面.xlsx（画面定義書、画面処理内容説明書）。API：docs/仕様/機能定義書-LMMVMV-API-02_30分値一覧取得API.xlsx（機能定義、機能説明、データ項目更新仕様説明書）。</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="28" customHeight="1">
+    <x:row r="28" ht="37.5" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>訂正済み項目</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
-        <x:v>ARVE_OFFICE_CODE=事業所コード、ARVE_CUSTOMER_NUMBER=お客さま番号。ユーザー指示で設計書を訂正済み。</x:v>
+        <x:v>ARVE_OFFICE_CODEは事業所コード、ARVE_CUSTOMER_NUMBERはお客さま番号を示す。設計書のレスポンス項目名はユーザーの指示に従って訂正済みである。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="37.5" customHeight="1">
